--- a/JPM.xlsx
+++ b/JPM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F73B71-E31F-4346-A543-3AF17C3597F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C01F14-6CAE-4AB5-A2A4-901D675C6845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39050" yWindow="2980" windowWidth="24340" windowHeight="15680" xr2:uid="{6FF43043-9969-4618-AD8F-D77E99073F78}"/>
+    <workbookView xWindow="21360" yWindow="4600" windowWidth="24170" windowHeight="12950" activeTab="1" xr2:uid="{6FF43043-9969-4618-AD8F-D77E99073F78}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
   <si>
     <t>Price</t>
   </si>
@@ -172,6 +172,51 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Consumer Banking &amp; Wealth Management</t>
+  </si>
+  <si>
+    <t>Consumer Home Lending</t>
+  </si>
+  <si>
+    <t>Consumer Card Services &amp; Auto</t>
+  </si>
+  <si>
+    <t>Investment Banking</t>
+  </si>
+  <si>
+    <t>Commercial Payments</t>
+  </si>
+  <si>
+    <t>Commercial Lending</t>
+  </si>
+  <si>
+    <t>Securities Services</t>
+  </si>
+  <si>
+    <t>Equities</t>
+  </si>
+  <si>
+    <t>Fixed Income</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Global Private Bank</t>
   </si>
 </sst>
 </file>
@@ -276,16 +321,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>11043</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>93869</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>44174</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>11043</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>132521</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>93869</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>88347</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -300,8 +345,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13268739" y="44174"/>
-          <a:ext cx="0" cy="7989956"/>
+          <a:off x="15781130" y="0"/>
+          <a:ext cx="0" cy="8823738"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -665,7 +710,7 @@
         <v>3</v>
       </c>
       <c r="K5" s="2">
-        <f>+Model!T5+Model!T6+Model!T8+Model!T9+Model!T10+Model!T11</f>
+        <f>+Model!T17+Model!T18+Model!T20+Model!T21+Model!T22+Model!T23</f>
         <v>3667137</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -677,7 +722,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="2">
-        <f>Model!T18+Model!T20+Model!T21</f>
+        <f>Model!T30+Model!T32+Model!T33</f>
         <v>3268877</v>
       </c>
       <c r="L6" s="4" t="s">
@@ -700,22 +745,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C14C4F3A-0E9F-4DB7-B175-0A62FF848762}">
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="2" max="2" width="26.7265625" customWidth="1"/>
     <col min="3" max="9" width="9.1796875" style="4"/>
     <col min="10" max="10" width="9.54296875" style="4" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
@@ -776,181 +821,615 @@
       <c r="V4" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" ht="13" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
+      <c r="W4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6">
+        <v>10324</v>
+      </c>
+      <c r="P5" s="6">
+        <v>10375</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>10090</v>
+      </c>
+      <c r="R5" s="6">
+        <f>40943-Q5-P5-O5</f>
+        <v>10154</v>
+      </c>
+      <c r="S5" s="6">
+        <v>10254</v>
+      </c>
+      <c r="T5" s="6">
+        <v>10698</v>
+      </c>
+      <c r="U5" s="6">
+        <v>11040</v>
+      </c>
+      <c r="V5" s="6">
+        <f>42862-U5-T5-S5</f>
+        <v>10870</v>
+      </c>
+      <c r="W5" s="6">
+        <v>10577</v>
+      </c>
+      <c r="X5" s="6">
+        <v>11229</v>
+      </c>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
+    </row>
+    <row r="6" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6">
+        <v>1186</v>
+      </c>
+      <c r="P6" s="6">
+        <v>1319</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>1295</v>
+      </c>
+      <c r="R6" s="6">
+        <f>5097-Q6-P6-O6</f>
+        <v>1297</v>
+      </c>
+      <c r="S6" s="6">
+        <v>1207</v>
+      </c>
+      <c r="T6" s="6">
+        <v>1250</v>
+      </c>
+      <c r="U6" s="6">
+        <v>1260</v>
+      </c>
+      <c r="V6" s="6">
+        <f>4966-U6-T6-S6</f>
+        <v>1249</v>
+      </c>
+      <c r="W6" s="6">
+        <v>1232</v>
+      </c>
+      <c r="X6" s="6">
+        <v>1285</v>
+      </c>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
+    </row>
+    <row r="7" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6">
+        <v>6143</v>
+      </c>
+      <c r="P7" s="6">
+        <v>6007</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>6406</v>
+      </c>
+      <c r="R7" s="6">
+        <f>25467-Q7-P7-O7</f>
+        <v>6911</v>
+      </c>
+      <c r="S7" s="6">
+        <v>6852</v>
+      </c>
+      <c r="T7" s="6">
+        <v>6899</v>
+      </c>
+      <c r="U7" s="6">
+        <v>7173</v>
+      </c>
+      <c r="V7" s="6">
+        <f>28201-U7-T7-S7</f>
+        <v>7277</v>
+      </c>
+      <c r="W7" s="6">
+        <v>7759</v>
+      </c>
+      <c r="X7" s="6">
+        <v>7758</v>
+      </c>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+    </row>
+    <row r="8" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6">
+        <v>2216</v>
+      </c>
+      <c r="P8" s="6">
+        <v>2464</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>2354</v>
+      </c>
+      <c r="R8" s="6">
+        <f>9636-Q8-P8-O8</f>
+        <v>2602</v>
+      </c>
+      <c r="S8" s="6">
+        <v>2268</v>
+      </c>
+      <c r="T8" s="6">
+        <v>2684</v>
+      </c>
+      <c r="U8" s="6">
+        <v>2694</v>
+      </c>
+      <c r="V8" s="6">
+        <f>10198-U8-T8-S8</f>
+        <v>2552</v>
+      </c>
+      <c r="W8" s="6">
+        <v>3136</v>
+      </c>
+      <c r="X8" s="6">
+        <v>3902</v>
+      </c>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+    </row>
+    <row r="9" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6">
+        <v>4466</v>
+      </c>
+      <c r="P9" s="6">
+        <v>4546</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>4370</v>
+      </c>
+      <c r="R9" s="6">
+        <f>18085-Q9-P9-O9</f>
+        <v>4703</v>
+      </c>
+      <c r="S9" s="6">
+        <v>4565</v>
+      </c>
+      <c r="T9" s="6">
+        <v>4735</v>
+      </c>
+      <c r="U9" s="6">
+        <v>4917</v>
+      </c>
+      <c r="V9" s="6">
+        <f>19331-U9-T9-S9</f>
+        <v>5114</v>
+      </c>
+      <c r="W9" s="6">
+        <v>5123</v>
+      </c>
+      <c r="X9" s="6">
+        <v>5296</v>
+      </c>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+    </row>
+    <row r="10" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6">
+        <v>1724</v>
+      </c>
+      <c r="P10" s="6">
+        <v>1936</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>1894</v>
+      </c>
+      <c r="R10" s="6">
+        <f>7470-Q10-P10-O10</f>
+        <v>1916</v>
+      </c>
+      <c r="S10" s="6">
+        <v>1915</v>
+      </c>
+      <c r="T10" s="6">
+        <v>1829</v>
+      </c>
+      <c r="U10" s="6">
+        <v>1872</v>
+      </c>
+      <c r="V10" s="6">
+        <f>7601-U10-T10-S10</f>
+        <v>1985</v>
+      </c>
+      <c r="W10" s="6">
+        <v>2166</v>
+      </c>
+      <c r="X10" s="6">
+        <v>1964</v>
+      </c>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+    </row>
+    <row r="11" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6">
+        <v>5428</v>
+      </c>
+      <c r="P11" s="6">
+        <v>4981</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>4651</v>
+      </c>
+      <c r="R11" s="6">
+        <f>20066-Q11-P11-O11</f>
+        <v>5006</v>
+      </c>
+      <c r="S11" s="6">
+        <v>5849</v>
+      </c>
+      <c r="T11" s="6">
+        <v>5690</v>
+      </c>
+      <c r="U11" s="6">
+        <v>5613</v>
+      </c>
+      <c r="V11" s="6">
+        <f>22532-U11-T11-S11</f>
+        <v>5380</v>
+      </c>
+      <c r="W11" s="6">
+        <v>7078</v>
+      </c>
+      <c r="X11" s="6">
+        <v>6053</v>
+      </c>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+    </row>
+    <row r="12" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6">
+        <v>2585</v>
+      </c>
+      <c r="P12" s="6">
+        <v>2812</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>2501</v>
+      </c>
+      <c r="R12" s="6">
+        <f>9941-Q12-P12-O12</f>
+        <v>2043</v>
+      </c>
+      <c r="S12" s="6">
+        <v>3814</v>
+      </c>
+      <c r="T12" s="6">
+        <v>3246</v>
+      </c>
+      <c r="U12" s="6">
+        <v>3331</v>
+      </c>
+      <c r="V12" s="6">
+        <f>13250-U12-T12-S12</f>
+        <v>2859</v>
+      </c>
+      <c r="W12" s="6">
+        <v>4481</v>
+      </c>
+      <c r="X12" s="6">
+        <v>6025</v>
+      </c>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+    </row>
+    <row r="13" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6">
+        <v>1183</v>
+      </c>
+      <c r="P13" s="6">
+        <v>1261</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>1326</v>
+      </c>
+      <c r="R13" s="6">
+        <f>5084-Q13-P13-O13</f>
+        <v>1314</v>
+      </c>
+      <c r="S13" s="6">
+        <v>1269</v>
+      </c>
+      <c r="T13" s="6">
+        <v>1418</v>
+      </c>
+      <c r="U13" s="6">
+        <v>1423</v>
+      </c>
+      <c r="V13" s="6">
+        <f>5599-U13-T13-S13</f>
+        <v>1489</v>
+      </c>
+      <c r="W13" s="6">
+        <v>1499</v>
+      </c>
+      <c r="X13" s="6">
+        <v>1657</v>
+      </c>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+    </row>
+    <row r="14" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6">
+        <v>2326</v>
+      </c>
+      <c r="P14" s="6">
+        <v>2437</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>2525</v>
+      </c>
+      <c r="R14" s="6">
+        <f>10175-Q14-P14-O14</f>
+        <v>2887</v>
+      </c>
+      <c r="S14" s="6">
+        <v>2671</v>
+      </c>
+      <c r="T14" s="6">
+        <v>2705</v>
+      </c>
+      <c r="U14" s="6">
+        <v>2916</v>
+      </c>
+      <c r="V14" s="6">
+        <f>11700-U14-T14-S14</f>
+        <v>3408</v>
+      </c>
+      <c r="W14" s="2">
+        <v>3072</v>
+      </c>
+      <c r="X14" s="2">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6">
+        <v>2783</v>
+      </c>
+      <c r="P15" s="6">
+        <v>2815</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>2914</v>
+      </c>
+      <c r="R15" s="6">
+        <f>11403-Q15-P15-O15</f>
+        <v>2891</v>
+      </c>
+      <c r="S15" s="6">
+        <v>3060</v>
+      </c>
+      <c r="T15" s="6">
+        <v>3055</v>
+      </c>
+      <c r="U15" s="6">
+        <v>3150</v>
+      </c>
+      <c r="V15" s="6">
+        <f>12373-U15-T15-S15</f>
+        <v>3108</v>
+      </c>
+      <c r="W15" s="2">
+        <v>3302</v>
+      </c>
+      <c r="X15" s="6">
+        <v>3531</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+    </row>
+    <row r="17" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J17" s="7">
         <v>27697</v>
       </c>
-      <c r="T5" s="7">
+      <c r="T17" s="7">
         <v>23759</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" ht="13" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="7">
-        <v>539537</v>
-      </c>
-      <c r="T6" s="7">
-        <v>396568</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="11">
-        <v>315592</v>
-      </c>
-      <c r="T7" s="11">
-        <v>470589</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="7">
-        <v>185369</v>
-      </c>
-      <c r="T8" s="7">
-        <v>223976</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="7">
-        <v>453799</v>
-      </c>
-      <c r="T9" s="7">
-        <v>889856</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="13" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="7">
-        <f>205857+425305</f>
-        <v>631162</v>
-      </c>
-      <c r="T10" s="7">
-        <f>485380+260559</f>
-        <v>745939</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="13" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="7">
-        <v>1115921</v>
-      </c>
-      <c r="T11" s="7">
-        <v>1387039</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="6">
-        <v>125189</v>
-      </c>
-      <c r="T12" s="6">
-        <v>124463</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="6">
-        <v>27734</v>
-      </c>
-      <c r="T13" s="6">
-        <v>33562</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="6">
-        <v>60859</v>
-      </c>
-      <c r="T14" s="6">
-        <v>64465</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="6">
-        <v>182884</v>
-      </c>
-      <c r="T15" s="6">
-        <v>192266</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="13" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" s="7">
-        <f>SUM(J5:J15)</f>
-        <v>3665743</v>
-      </c>
-      <c r="T16" s="7">
-        <f>SUM(T5:T15)</f>
-        <v>4552482</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="T17" s="4"/>
     </row>
     <row r="18" spans="2:20" ht="13" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="6">
-        <v>2340179</v>
+      <c r="J18" s="7">
+        <v>539537</v>
       </c>
       <c r="T18" s="7">
-        <v>2562380</v>
+        <v>396568</v>
       </c>
     </row>
     <row r="19" spans="2:20" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B19" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -960,15 +1439,15 @@
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
       <c r="J19" s="11">
-        <v>202613</v>
+        <v>315592</v>
       </c>
       <c r="T19" s="11">
-        <v>595340</v>
+        <v>470589</v>
       </c>
     </row>
     <row r="20" spans="2:20" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -978,17 +1457,15 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="7">
-        <f>44027+295865</f>
-        <v>339892</v>
+        <v>185369</v>
       </c>
       <c r="T20" s="7">
-        <f>419802+65293</f>
-        <v>485095</v>
+        <v>223976</v>
       </c>
     </row>
     <row r="21" spans="2:20" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -998,74 +1475,225 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="7">
+        <v>453799</v>
+      </c>
+      <c r="T21" s="7">
+        <v>889856</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="B22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="7">
+        <f>205857+425305</f>
+        <v>631162</v>
+      </c>
+      <c r="T22" s="7">
+        <f>485380+260559</f>
+        <v>745939</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="B23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="7">
+        <v>1115921</v>
+      </c>
+      <c r="T23" s="7">
+        <v>1387039</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="6">
+        <v>125189</v>
+      </c>
+      <c r="T24" s="6">
+        <v>124463</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="6">
+        <v>27734</v>
+      </c>
+      <c r="T25" s="6">
+        <v>33562</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="6">
+        <v>60859</v>
+      </c>
+      <c r="T26" s="6">
+        <v>64465</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="6">
+        <v>182884</v>
+      </c>
+      <c r="T27" s="6">
+        <v>192266</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" s="7">
+        <f>SUM(J17:J27)</f>
+        <v>3665743</v>
+      </c>
+      <c r="T28" s="7">
+        <f>SUM(T17:T27)</f>
+        <v>4552482</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="T29" s="4"/>
+    </row>
+    <row r="30" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="B30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="6">
+        <v>2340179</v>
+      </c>
+      <c r="T30" s="7">
+        <v>2562380</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="11">
+        <v>202613</v>
+      </c>
+      <c r="T31" s="11">
+        <v>595340</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B32" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="7">
+        <f>44027+295865</f>
+        <v>339892</v>
+      </c>
+      <c r="T32" s="7">
+        <f>419802+65293</f>
+        <v>485095</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="7">
         <v>177976</v>
       </c>
-      <c r="T21" s="7">
+      <c r="T33" s="7">
         <v>221402</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>28</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J34" s="6">
         <v>300141</v>
       </c>
-      <c r="T22" s="6">
+      <c r="T34" s="6">
         <v>303641</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>29</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J35" s="4">
         <v>12610</v>
       </c>
-      <c r="T23" s="6">
+      <c r="T35" s="6">
         <v>27700</v>
       </c>
     </row>
-    <row r="24" spans="2:20" ht="13" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+    <row r="36" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
         <v>30</v>
       </c>
-      <c r="J24" s="7">
-        <f>SUM(J18:J23)</f>
+      <c r="J36" s="7">
+        <f>SUM(J30:J35)</f>
         <v>3373411</v>
       </c>
-      <c r="T24" s="7">
-        <f>SUM(T18:T23)</f>
+      <c r="T36" s="7">
+        <f>SUM(T30:T35)</f>
         <v>4195558</v>
       </c>
     </row>
-    <row r="25" spans="2:20" ht="13" x14ac:dyDescent="0.3">
-      <c r="J25" s="7"/>
-      <c r="T25" s="7"/>
-    </row>
-    <row r="26" spans="2:20" ht="13" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    <row r="37" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="J37" s="7"/>
+      <c r="T37" s="7"/>
+    </row>
+    <row r="38" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
         <v>31</v>
       </c>
-      <c r="J26" s="7">
-        <f>J16-J24</f>
+      <c r="J38" s="7">
+        <f>J28-J36</f>
         <v>292332</v>
       </c>
-      <c r="T26" s="7">
-        <f>T16-T24</f>
+      <c r="T38" s="7">
+        <f>T28-T36</f>
         <v>356924</v>
       </c>
     </row>
-    <row r="27" spans="2:20" ht="13" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+    <row r="39" spans="2:20" ht="13" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="7">
-        <f>J26-J14</f>
+      <c r="J39" s="7">
+        <f>J38-J26</f>
         <v>231473</v>
       </c>
-      <c r="T27" s="7">
-        <f>T26-T14</f>
+      <c r="T39" s="7">
+        <f>T38-T26</f>
         <v>292459</v>
       </c>
     </row>
